--- a/Result/profitability/5301.xlsx
+++ b/Result/profitability/5301.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2025</v>
+        <v>-0.22875</v>
       </c>
       <c r="N2" t="n">
-        <v>63.09125000000001</v>
+        <v>64.94625000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2025</v>
+        <v>-0.20625</v>
       </c>
       <c r="N3" t="n">
-        <v>55.59</v>
+        <v>58.88000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.12125</v>
+        <v>-0.135</v>
       </c>
       <c r="N4" t="n">
-        <v>49.50375</v>
+        <v>49.45500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1675</v>
+        <v>-0.1625</v>
       </c>
       <c r="N5" t="n">
-        <v>38.48500000000001</v>
+        <v>40.4325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.10375</v>
+        <v>-0.1175</v>
       </c>
       <c r="N6" t="n">
-        <v>29.69750000000001</v>
+        <v>30.07875000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-1.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.21625</v>
+        <v>-0.13875</v>
       </c>
       <c r="N7" t="n">
-        <v>19.62250000000001</v>
+        <v>25.75125000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.73</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.20125</v>
+        <v>-0.2075</v>
       </c>
       <c r="N8" t="n">
-        <v>15.41375</v>
+        <v>15.69125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>34</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="n">
+        <v>29</v>
+      </c>
+      <c r="F75" t="n">
+        <v>85.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-41.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.24875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>72.14875000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.05000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2777777777777779</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.219999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02650429799426934</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.04000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1481481481481481</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2213068181818181</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
